--- a/results/performance_metrics.xlsx
+++ b/results/performance_metrics.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.756898190075761</v>
+        <v>2.756898190075763</v>
       </c>
       <c r="C2" t="n">
         <v>29.46208811265443</v>
@@ -472,7 +472,7 @@
         <v>0.9929853088736995</v>
       </c>
       <c r="F2" t="n">
-        <v>3.83041969506476</v>
+        <v>3.830419695064761</v>
       </c>
       <c r="G2" t="n">
         <v>0.9930185283983181</v>
